--- a/Asset/Data guru dan siswa kuttab Agus 2026.xlsx
+++ b/Asset/Data guru dan siswa kuttab Agus 2026.xlsx
@@ -648,7 +648,7 @@
     <t>Hawa Sigit El karimah</t>
   </si>
   <si>
-    <t>Kairo Malik Sopyan</t>
+    <t>Kairo Malik Sofyan</t>
   </si>
   <si>
     <t>M Sa'ad Salim Hadwan Saputra</t>
@@ -666,7 +666,7 @@
     <t>Sabria Hafizul Azhar</t>
   </si>
   <si>
-    <t>Ufaira Afwa Khoirunnisa</t>
+    <t>Ufairah Afwa Khoirunnisa</t>
   </si>
   <si>
     <t>Kelas</t>

--- a/Asset/Data guru dan siswa kuttab Agus 2026.xlsx
+++ b/Asset/Data guru dan siswa kuttab Agus 2026.xlsx
@@ -2637,7 +2637,7 @@
         <v>187</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
@@ -2805,7 +2805,7 @@
         <v>208</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
